--- a/cl_st1_ph3_ednalvo/avaliacao_composicoes/comparacao_de_candidatos.xlsx
+++ b/cl_st1_ph3_ednalvo/avaliacao_composicoes/comparacao_de_candidatos.xlsx
@@ -424,152 +424,152 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>adequacao_a_coletanea_human_high</t>
+          <t>adequacao_a_coletanea_humano_maiores_notas</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>adequacao_a_coletanea_human_low</t>
+          <t>adequacao_a_coletanea_humano_menores_notas</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>adequacao_a_coletanea_gemini_low_mirror</t>
+          <t>adequacao_a_coletanea_gemini_menores_notas_espelho</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>adequacao_a_coletanea_gpt_low_mirror</t>
+          <t>adequacao_a_coletanea_gpt_menores_notas_espelho</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>adequacao_a_norma_padrao_human_high</t>
+          <t>adequacao_a_norma_padrao_humano_maiores_notas</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>adequacao_a_norma_padrao_human_low</t>
+          <t>adequacao_a_norma_padrao_humano_menores_notas</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>adequacao_a_norma_padrao_gemini_low_mirror</t>
+          <t>adequacao_a_norma_padrao_gemini_menores_notas_espelho</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>adequacao_a_norma_padrao_gpt_low_mirror</t>
+          <t>adequacao_a_norma_padrao_gpt_menores_notas_espelho</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>adequacao_ao_tema_human_high</t>
+          <t>adequacao_ao_tema_humano_maiores_notas</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>adequacao_ao_tema_human_low</t>
+          <t>adequacao_ao_tema_humano_menores_notas</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>adequacao_ao_tema_gemini_low_mirror</t>
+          <t>adequacao_ao_tema_gemini_menores_notas_espelho</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>adequacao_ao_tema_gpt_low_mirror</t>
+          <t>adequacao_ao_tema_gpt_menores_notas_espelho</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>adequacao_ao_tipo_de_texto_human_high</t>
+          <t>adequacao_ao_tipo_de_texto_humano_maiores_notas</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>adequacao_ao_tipo_de_texto_human_low</t>
+          <t>adequacao_ao_tipo_de_texto_humano_menores_notas</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>adequacao_ao_tipo_de_texto_gemini_low_mirror</t>
+          <t>adequacao_ao_tipo_de_texto_gemini_menores_notas_espelho</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>adequacao_ao_tipo_de_texto_gpt_low_mirror</t>
+          <t>adequacao_ao_tipo_de_texto_gpt_menores_notas_espelho</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>coerencia_human_high</t>
+          <t>coerencia_humano_maiores_notas</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>coerencia_human_low</t>
+          <t>coerencia_humano_menores_notas</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>coerencia_gemini_low_mirror</t>
+          <t>coerencia_gemini_menores_notas_espelho</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>coerencia_gpt_low_mirror</t>
+          <t>coerencia_gpt_menores_notas_espelho</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>coesao_human_high</t>
+          <t>coesao_humano_maiores_notas</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>coesao_human_low</t>
+          <t>coesao_humano_menores_notas</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>coesao_gemini_low_mirror</t>
+          <t>coesao_gemini_menores_notas_espelho</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>coesao_gpt_low_mirror</t>
+          <t>coesao_gpt_menores_notas_espelho</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>pontuacao_total_human_high</t>
+          <t>pontuacao_total_humano_maiores_notas</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>pontuacao_total_human_low</t>
+          <t>pontuacao_total_humano_menores_notas</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>pontuacao_total_gemini_low_mirror</t>
+          <t>pontuacao_total_gemini_menores_notas_espelho</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>pontuacao_total_gpt_low_mirror</t>
+          <t>pontuacao_total_gpt_menores_notas_espelho</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>gain_gemini_vs_human_low</t>
+          <t>gain_gemini_vs_humano_menores_notas</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>gain_gpt_vs_human_low</t>
+          <t>gain_gpt_vs_humano_menores_notas</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
